--- a/resources/variable_schema_data_individual_death_template.xlsx
+++ b/resources/variable_schema_data_individual_death_template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saeed.rahman\Desktop\public_health_resources\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DE869D9-F53E-470B-8E2F-8C60967D88BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48FF0CE0-9612-41C1-AD40-8B6ACCB9966D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14280" yWindow="0" windowWidth="14625" windowHeight="17385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1557" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2012" uniqueCount="521">
   <si>
     <t>rule_type</t>
   </si>
@@ -1469,6 +1469,120 @@
   </si>
   <si>
     <t>المنطقة الإدارية 4</t>
+  </si>
+  <si>
+    <t>0-4y,0-4</t>
+  </si>
+  <si>
+    <t>5-9y,5-9</t>
+  </si>
+  <si>
+    <t>10-14y,10-14</t>
+  </si>
+  <si>
+    <t>15-19y,15-19</t>
+  </si>
+  <si>
+    <t>20-24y,20-24</t>
+  </si>
+  <si>
+    <t>25-29y,25-29</t>
+  </si>
+  <si>
+    <t>30-34y,30-34</t>
+  </si>
+  <si>
+    <t>35-39y,35-39</t>
+  </si>
+  <si>
+    <t>40-44y,40-44</t>
+  </si>
+  <si>
+    <t>45-49y,45-49</t>
+  </si>
+  <si>
+    <t>50-54y</t>
+  </si>
+  <si>
+    <t>50-54y,50-54</t>
+  </si>
+  <si>
+    <t>55-59y</t>
+  </si>
+  <si>
+    <t>55-59y,55-59</t>
+  </si>
+  <si>
+    <t>60-64y,60-64</t>
+  </si>
+  <si>
+    <t>65-69y,65-69</t>
+  </si>
+  <si>
+    <t>70-74y,70-74</t>
+  </si>
+  <si>
+    <t>75-79y,75-79</t>
+  </si>
+  <si>
+    <t>80-84y,80-84</t>
+  </si>
+  <si>
+    <t>85-89y,85-89</t>
+  </si>
+  <si>
+    <t>90-94y,90-94</t>
+  </si>
+  <si>
+    <t>95-99y,95-99</t>
+  </si>
+  <si>
+    <t>100-104y,100-104</t>
+  </si>
+  <si>
+    <t>105-109y,105-109</t>
+  </si>
+  <si>
+    <t>110-114y,110-114</t>
+  </si>
+  <si>
+    <t>115-119y,115-119</t>
+  </si>
+  <si>
+    <t>120-124y,120-124</t>
+  </si>
+  <si>
+    <t>0-5m,0-5</t>
+  </si>
+  <si>
+    <t>6-11m,6-11</t>
+  </si>
+  <si>
+    <t>12-17m,12-17</t>
+  </si>
+  <si>
+    <t>18-23m</t>
+  </si>
+  <si>
+    <t>18-23m,18-23</t>
+  </si>
+  <si>
+    <t>24-29m,24-29</t>
+  </si>
+  <si>
+    <t>30-35m,30-35</t>
+  </si>
+  <si>
+    <t>36-41m,36-41</t>
+  </si>
+  <si>
+    <t>42-47m,42-47</t>
+  </si>
+  <si>
+    <t>48-53m,48-53</t>
+  </si>
+  <si>
+    <t>54-59m,54-59</t>
   </si>
 </sst>
 </file>
@@ -1510,7 +1624,27 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="21">
+  <dxfs count="23">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2019,7 +2153,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S139"/>
+  <dimension ref="A1:S174"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="26.5703125" customWidth="1"/>
@@ -6796,7 +6930,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>1</v>
       </c>
@@ -6822,7 +6956,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>1</v>
       </c>
@@ -6848,7 +6982,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>1</v>
       </c>
@@ -6874,7 +7008,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>1</v>
       </c>
@@ -6900,7 +7034,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>1</v>
       </c>
@@ -6926,7 +7060,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>1</v>
       </c>
@@ -6952,7 +7086,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>1</v>
       </c>
@@ -6978,7 +7112,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>1</v>
       </c>
@@ -7004,7 +7138,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>1</v>
       </c>
@@ -7030,7 +7164,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>1</v>
       </c>
@@ -7056,7 +7190,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>1</v>
       </c>
@@ -7082,69 +7216,1510 @@
         <v>410</v>
       </c>
     </row>
+    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>1</v>
+      </c>
+      <c r="B140" t="s">
+        <v>286</v>
+      </c>
+      <c r="C140" t="s">
+        <v>287</v>
+      </c>
+      <c r="E140" t="s">
+        <v>288</v>
+      </c>
+      <c r="F140" t="s">
+        <v>43</v>
+      </c>
+      <c r="I140" t="s">
+        <v>483</v>
+      </c>
+      <c r="J140" t="s">
+        <v>286</v>
+      </c>
+      <c r="L140" t="s">
+        <v>290</v>
+      </c>
+      <c r="M140" t="s">
+        <v>291</v>
+      </c>
+      <c r="N140" t="s">
+        <v>292</v>
+      </c>
+      <c r="O140" t="s">
+        <v>287</v>
+      </c>
+      <c r="P140" t="s">
+        <v>287</v>
+      </c>
+      <c r="Q140" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>1</v>
+      </c>
+      <c r="B141" t="s">
+        <v>286</v>
+      </c>
+      <c r="C141" t="s">
+        <v>293</v>
+      </c>
+      <c r="E141" t="s">
+        <v>288</v>
+      </c>
+      <c r="F141" t="s">
+        <v>43</v>
+      </c>
+      <c r="I141" t="s">
+        <v>484</v>
+      </c>
+      <c r="J141" t="s">
+        <v>286</v>
+      </c>
+      <c r="L141" t="s">
+        <v>290</v>
+      </c>
+      <c r="M141" t="s">
+        <v>291</v>
+      </c>
+      <c r="N141" t="s">
+        <v>292</v>
+      </c>
+      <c r="O141" t="s">
+        <v>293</v>
+      </c>
+      <c r="P141" t="s">
+        <v>293</v>
+      </c>
+      <c r="Q141" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>1</v>
+      </c>
+      <c r="B142" t="s">
+        <v>286</v>
+      </c>
+      <c r="C142" t="s">
+        <v>295</v>
+      </c>
+      <c r="E142" t="s">
+        <v>288</v>
+      </c>
+      <c r="F142" t="s">
+        <v>43</v>
+      </c>
+      <c r="I142" t="s">
+        <v>485</v>
+      </c>
+      <c r="J142" t="s">
+        <v>286</v>
+      </c>
+      <c r="L142" t="s">
+        <v>290</v>
+      </c>
+      <c r="M142" t="s">
+        <v>291</v>
+      </c>
+      <c r="N142" t="s">
+        <v>292</v>
+      </c>
+      <c r="O142" t="s">
+        <v>295</v>
+      </c>
+      <c r="P142" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q142" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>1</v>
+      </c>
+      <c r="B143" t="s">
+        <v>286</v>
+      </c>
+      <c r="C143" t="s">
+        <v>297</v>
+      </c>
+      <c r="E143" t="s">
+        <v>288</v>
+      </c>
+      <c r="F143" t="s">
+        <v>43</v>
+      </c>
+      <c r="I143" t="s">
+        <v>486</v>
+      </c>
+      <c r="J143" t="s">
+        <v>286</v>
+      </c>
+      <c r="L143" t="s">
+        <v>290</v>
+      </c>
+      <c r="M143" t="s">
+        <v>291</v>
+      </c>
+      <c r="N143" t="s">
+        <v>292</v>
+      </c>
+      <c r="O143" t="s">
+        <v>297</v>
+      </c>
+      <c r="P143" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q143" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>1</v>
+      </c>
+      <c r="B144" t="s">
+        <v>286</v>
+      </c>
+      <c r="C144" t="s">
+        <v>299</v>
+      </c>
+      <c r="E144" t="s">
+        <v>288</v>
+      </c>
+      <c r="F144" t="s">
+        <v>43</v>
+      </c>
+      <c r="I144" t="s">
+        <v>487</v>
+      </c>
+      <c r="J144" t="s">
+        <v>286</v>
+      </c>
+      <c r="L144" t="s">
+        <v>290</v>
+      </c>
+      <c r="M144" t="s">
+        <v>291</v>
+      </c>
+      <c r="N144" t="s">
+        <v>292</v>
+      </c>
+      <c r="O144" t="s">
+        <v>299</v>
+      </c>
+      <c r="P144" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q144" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>1</v>
+      </c>
+      <c r="B145" t="s">
+        <v>286</v>
+      </c>
+      <c r="C145" t="s">
+        <v>301</v>
+      </c>
+      <c r="E145" t="s">
+        <v>288</v>
+      </c>
+      <c r="F145" t="s">
+        <v>43</v>
+      </c>
+      <c r="I145" t="s">
+        <v>488</v>
+      </c>
+      <c r="J145" t="s">
+        <v>286</v>
+      </c>
+      <c r="L145" t="s">
+        <v>290</v>
+      </c>
+      <c r="M145" t="s">
+        <v>291</v>
+      </c>
+      <c r="N145" t="s">
+        <v>292</v>
+      </c>
+      <c r="O145" t="s">
+        <v>301</v>
+      </c>
+      <c r="P145" t="s">
+        <v>301</v>
+      </c>
+      <c r="Q145" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>1</v>
+      </c>
+      <c r="B146" t="s">
+        <v>286</v>
+      </c>
+      <c r="C146" t="s">
+        <v>303</v>
+      </c>
+      <c r="E146" t="s">
+        <v>288</v>
+      </c>
+      <c r="F146" t="s">
+        <v>43</v>
+      </c>
+      <c r="I146" t="s">
+        <v>489</v>
+      </c>
+      <c r="J146" t="s">
+        <v>286</v>
+      </c>
+      <c r="L146" t="s">
+        <v>290</v>
+      </c>
+      <c r="M146" t="s">
+        <v>291</v>
+      </c>
+      <c r="N146" t="s">
+        <v>292</v>
+      </c>
+      <c r="O146" t="s">
+        <v>303</v>
+      </c>
+      <c r="P146" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q146" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>1</v>
+      </c>
+      <c r="B147" t="s">
+        <v>286</v>
+      </c>
+      <c r="C147" t="s">
+        <v>305</v>
+      </c>
+      <c r="E147" t="s">
+        <v>288</v>
+      </c>
+      <c r="F147" t="s">
+        <v>43</v>
+      </c>
+      <c r="I147" t="s">
+        <v>490</v>
+      </c>
+      <c r="J147" t="s">
+        <v>286</v>
+      </c>
+      <c r="L147" t="s">
+        <v>290</v>
+      </c>
+      <c r="M147" t="s">
+        <v>291</v>
+      </c>
+      <c r="N147" t="s">
+        <v>292</v>
+      </c>
+      <c r="O147" t="s">
+        <v>305</v>
+      </c>
+      <c r="P147" t="s">
+        <v>305</v>
+      </c>
+      <c r="Q147" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>1</v>
+      </c>
+      <c r="B148" t="s">
+        <v>286</v>
+      </c>
+      <c r="C148" t="s">
+        <v>307</v>
+      </c>
+      <c r="E148" t="s">
+        <v>288</v>
+      </c>
+      <c r="F148" t="s">
+        <v>43</v>
+      </c>
+      <c r="I148" t="s">
+        <v>491</v>
+      </c>
+      <c r="J148" t="s">
+        <v>286</v>
+      </c>
+      <c r="L148" t="s">
+        <v>290</v>
+      </c>
+      <c r="M148" t="s">
+        <v>291</v>
+      </c>
+      <c r="N148" t="s">
+        <v>292</v>
+      </c>
+      <c r="O148" t="s">
+        <v>307</v>
+      </c>
+      <c r="P148" t="s">
+        <v>307</v>
+      </c>
+      <c r="Q148" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>1</v>
+      </c>
+      <c r="B149" t="s">
+        <v>286</v>
+      </c>
+      <c r="C149" t="s">
+        <v>309</v>
+      </c>
+      <c r="E149" t="s">
+        <v>288</v>
+      </c>
+      <c r="F149" t="s">
+        <v>43</v>
+      </c>
+      <c r="I149" t="s">
+        <v>492</v>
+      </c>
+      <c r="J149" t="s">
+        <v>286</v>
+      </c>
+      <c r="L149" t="s">
+        <v>290</v>
+      </c>
+      <c r="M149" t="s">
+        <v>291</v>
+      </c>
+      <c r="N149" t="s">
+        <v>292</v>
+      </c>
+      <c r="O149" t="s">
+        <v>309</v>
+      </c>
+      <c r="P149" t="s">
+        <v>309</v>
+      </c>
+      <c r="Q149" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>1</v>
+      </c>
+      <c r="B150" t="s">
+        <v>286</v>
+      </c>
+      <c r="C150" t="s">
+        <v>493</v>
+      </c>
+      <c r="E150" t="s">
+        <v>288</v>
+      </c>
+      <c r="F150" t="s">
+        <v>43</v>
+      </c>
+      <c r="I150" t="s">
+        <v>494</v>
+      </c>
+      <c r="J150" t="s">
+        <v>286</v>
+      </c>
+      <c r="L150" t="s">
+        <v>290</v>
+      </c>
+      <c r="M150" t="s">
+        <v>291</v>
+      </c>
+      <c r="N150" t="s">
+        <v>292</v>
+      </c>
+      <c r="O150" t="s">
+        <v>493</v>
+      </c>
+      <c r="P150" t="s">
+        <v>493</v>
+      </c>
+      <c r="Q150" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>1</v>
+      </c>
+      <c r="B151" t="s">
+        <v>286</v>
+      </c>
+      <c r="C151" t="s">
+        <v>495</v>
+      </c>
+      <c r="E151" t="s">
+        <v>288</v>
+      </c>
+      <c r="F151" t="s">
+        <v>43</v>
+      </c>
+      <c r="I151" t="s">
+        <v>496</v>
+      </c>
+      <c r="J151" t="s">
+        <v>286</v>
+      </c>
+      <c r="L151" t="s">
+        <v>290</v>
+      </c>
+      <c r="M151" t="s">
+        <v>291</v>
+      </c>
+      <c r="N151" t="s">
+        <v>292</v>
+      </c>
+      <c r="O151" t="s">
+        <v>495</v>
+      </c>
+      <c r="P151" t="s">
+        <v>495</v>
+      </c>
+      <c r="Q151" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>1</v>
+      </c>
+      <c r="B152" t="s">
+        <v>286</v>
+      </c>
+      <c r="C152" t="s">
+        <v>313</v>
+      </c>
+      <c r="E152" t="s">
+        <v>288</v>
+      </c>
+      <c r="F152" t="s">
+        <v>43</v>
+      </c>
+      <c r="I152" t="s">
+        <v>497</v>
+      </c>
+      <c r="J152" t="s">
+        <v>286</v>
+      </c>
+      <c r="L152" t="s">
+        <v>290</v>
+      </c>
+      <c r="M152" t="s">
+        <v>291</v>
+      </c>
+      <c r="N152" t="s">
+        <v>292</v>
+      </c>
+      <c r="O152" t="s">
+        <v>313</v>
+      </c>
+      <c r="P152" t="s">
+        <v>313</v>
+      </c>
+      <c r="Q152" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>1</v>
+      </c>
+      <c r="B153" t="s">
+        <v>286</v>
+      </c>
+      <c r="C153" t="s">
+        <v>315</v>
+      </c>
+      <c r="E153" t="s">
+        <v>288</v>
+      </c>
+      <c r="F153" t="s">
+        <v>43</v>
+      </c>
+      <c r="I153" t="s">
+        <v>498</v>
+      </c>
+      <c r="J153" t="s">
+        <v>286</v>
+      </c>
+      <c r="L153" t="s">
+        <v>290</v>
+      </c>
+      <c r="M153" t="s">
+        <v>291</v>
+      </c>
+      <c r="N153" t="s">
+        <v>292</v>
+      </c>
+      <c r="O153" t="s">
+        <v>315</v>
+      </c>
+      <c r="P153" t="s">
+        <v>315</v>
+      </c>
+      <c r="Q153" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>1</v>
+      </c>
+      <c r="B154" t="s">
+        <v>286</v>
+      </c>
+      <c r="C154" t="s">
+        <v>317</v>
+      </c>
+      <c r="E154" t="s">
+        <v>288</v>
+      </c>
+      <c r="F154" t="s">
+        <v>43</v>
+      </c>
+      <c r="I154" t="s">
+        <v>499</v>
+      </c>
+      <c r="J154" t="s">
+        <v>286</v>
+      </c>
+      <c r="L154" t="s">
+        <v>290</v>
+      </c>
+      <c r="M154" t="s">
+        <v>291</v>
+      </c>
+      <c r="N154" t="s">
+        <v>292</v>
+      </c>
+      <c r="O154" t="s">
+        <v>317</v>
+      </c>
+      <c r="P154" t="s">
+        <v>317</v>
+      </c>
+      <c r="Q154" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>1</v>
+      </c>
+      <c r="B155" t="s">
+        <v>286</v>
+      </c>
+      <c r="C155" t="s">
+        <v>319</v>
+      </c>
+      <c r="E155" t="s">
+        <v>288</v>
+      </c>
+      <c r="F155" t="s">
+        <v>43</v>
+      </c>
+      <c r="I155" t="s">
+        <v>500</v>
+      </c>
+      <c r="J155" t="s">
+        <v>286</v>
+      </c>
+      <c r="L155" t="s">
+        <v>290</v>
+      </c>
+      <c r="M155" t="s">
+        <v>291</v>
+      </c>
+      <c r="N155" t="s">
+        <v>292</v>
+      </c>
+      <c r="O155" t="s">
+        <v>319</v>
+      </c>
+      <c r="P155" t="s">
+        <v>319</v>
+      </c>
+      <c r="Q155" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>1</v>
+      </c>
+      <c r="B156" t="s">
+        <v>286</v>
+      </c>
+      <c r="C156" t="s">
+        <v>321</v>
+      </c>
+      <c r="E156" t="s">
+        <v>288</v>
+      </c>
+      <c r="F156" t="s">
+        <v>43</v>
+      </c>
+      <c r="I156" t="s">
+        <v>501</v>
+      </c>
+      <c r="J156" t="s">
+        <v>286</v>
+      </c>
+      <c r="L156" t="s">
+        <v>290</v>
+      </c>
+      <c r="M156" t="s">
+        <v>291</v>
+      </c>
+      <c r="N156" t="s">
+        <v>292</v>
+      </c>
+      <c r="O156" t="s">
+        <v>321</v>
+      </c>
+      <c r="P156" t="s">
+        <v>321</v>
+      </c>
+      <c r="Q156" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>1</v>
+      </c>
+      <c r="B157" t="s">
+        <v>286</v>
+      </c>
+      <c r="C157" t="s">
+        <v>323</v>
+      </c>
+      <c r="E157" t="s">
+        <v>288</v>
+      </c>
+      <c r="F157" t="s">
+        <v>43</v>
+      </c>
+      <c r="I157" t="s">
+        <v>502</v>
+      </c>
+      <c r="J157" t="s">
+        <v>286</v>
+      </c>
+      <c r="L157" t="s">
+        <v>290</v>
+      </c>
+      <c r="M157" t="s">
+        <v>291</v>
+      </c>
+      <c r="N157" t="s">
+        <v>292</v>
+      </c>
+      <c r="O157" t="s">
+        <v>323</v>
+      </c>
+      <c r="P157" t="s">
+        <v>323</v>
+      </c>
+      <c r="Q157" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>1</v>
+      </c>
+      <c r="B158" t="s">
+        <v>286</v>
+      </c>
+      <c r="C158" t="s">
+        <v>325</v>
+      </c>
+      <c r="E158" t="s">
+        <v>288</v>
+      </c>
+      <c r="F158" t="s">
+        <v>43</v>
+      </c>
+      <c r="I158" t="s">
+        <v>503</v>
+      </c>
+      <c r="J158" t="s">
+        <v>286</v>
+      </c>
+      <c r="L158" t="s">
+        <v>290</v>
+      </c>
+      <c r="M158" t="s">
+        <v>291</v>
+      </c>
+      <c r="N158" t="s">
+        <v>292</v>
+      </c>
+      <c r="O158" t="s">
+        <v>325</v>
+      </c>
+      <c r="P158" t="s">
+        <v>325</v>
+      </c>
+      <c r="Q158" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>1</v>
+      </c>
+      <c r="B159" t="s">
+        <v>286</v>
+      </c>
+      <c r="C159" t="s">
+        <v>327</v>
+      </c>
+      <c r="E159" t="s">
+        <v>288</v>
+      </c>
+      <c r="F159" t="s">
+        <v>43</v>
+      </c>
+      <c r="I159" t="s">
+        <v>504</v>
+      </c>
+      <c r="J159" t="s">
+        <v>286</v>
+      </c>
+      <c r="L159" t="s">
+        <v>290</v>
+      </c>
+      <c r="M159" t="s">
+        <v>291</v>
+      </c>
+      <c r="N159" t="s">
+        <v>292</v>
+      </c>
+      <c r="O159" t="s">
+        <v>327</v>
+      </c>
+      <c r="P159" t="s">
+        <v>327</v>
+      </c>
+      <c r="Q159" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>1</v>
+      </c>
+      <c r="B160" t="s">
+        <v>286</v>
+      </c>
+      <c r="C160" t="s">
+        <v>329</v>
+      </c>
+      <c r="E160" t="s">
+        <v>288</v>
+      </c>
+      <c r="F160" t="s">
+        <v>43</v>
+      </c>
+      <c r="I160" t="s">
+        <v>505</v>
+      </c>
+      <c r="J160" t="s">
+        <v>286</v>
+      </c>
+      <c r="L160" t="s">
+        <v>290</v>
+      </c>
+      <c r="M160" t="s">
+        <v>291</v>
+      </c>
+      <c r="N160" t="s">
+        <v>292</v>
+      </c>
+      <c r="O160" t="s">
+        <v>329</v>
+      </c>
+      <c r="P160" t="s">
+        <v>329</v>
+      </c>
+      <c r="Q160" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="161" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>1</v>
+      </c>
+      <c r="B161" t="s">
+        <v>286</v>
+      </c>
+      <c r="C161" t="s">
+        <v>331</v>
+      </c>
+      <c r="E161" t="s">
+        <v>288</v>
+      </c>
+      <c r="F161" t="s">
+        <v>43</v>
+      </c>
+      <c r="I161" t="s">
+        <v>506</v>
+      </c>
+      <c r="J161" t="s">
+        <v>286</v>
+      </c>
+      <c r="L161" t="s">
+        <v>290</v>
+      </c>
+      <c r="M161" t="s">
+        <v>291</v>
+      </c>
+      <c r="N161" t="s">
+        <v>292</v>
+      </c>
+      <c r="O161" t="s">
+        <v>331</v>
+      </c>
+      <c r="P161" t="s">
+        <v>331</v>
+      </c>
+      <c r="Q161" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>1</v>
+      </c>
+      <c r="B162" t="s">
+        <v>286</v>
+      </c>
+      <c r="C162" t="s">
+        <v>333</v>
+      </c>
+      <c r="E162" t="s">
+        <v>288</v>
+      </c>
+      <c r="F162" t="s">
+        <v>43</v>
+      </c>
+      <c r="I162" t="s">
+        <v>507</v>
+      </c>
+      <c r="J162" t="s">
+        <v>286</v>
+      </c>
+      <c r="L162" t="s">
+        <v>290</v>
+      </c>
+      <c r="M162" t="s">
+        <v>291</v>
+      </c>
+      <c r="N162" t="s">
+        <v>292</v>
+      </c>
+      <c r="O162" t="s">
+        <v>333</v>
+      </c>
+      <c r="P162" t="s">
+        <v>333</v>
+      </c>
+      <c r="Q162" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="163" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>1</v>
+      </c>
+      <c r="B163" t="s">
+        <v>286</v>
+      </c>
+      <c r="C163" t="s">
+        <v>335</v>
+      </c>
+      <c r="E163" t="s">
+        <v>288</v>
+      </c>
+      <c r="F163" t="s">
+        <v>43</v>
+      </c>
+      <c r="I163" t="s">
+        <v>508</v>
+      </c>
+      <c r="J163" t="s">
+        <v>286</v>
+      </c>
+      <c r="L163" t="s">
+        <v>290</v>
+      </c>
+      <c r="M163" t="s">
+        <v>291</v>
+      </c>
+      <c r="N163" t="s">
+        <v>292</v>
+      </c>
+      <c r="O163" t="s">
+        <v>335</v>
+      </c>
+      <c r="P163" t="s">
+        <v>335</v>
+      </c>
+      <c r="Q163" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="164" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>1</v>
+      </c>
+      <c r="B164" t="s">
+        <v>286</v>
+      </c>
+      <c r="C164" t="s">
+        <v>337</v>
+      </c>
+      <c r="E164" t="s">
+        <v>288</v>
+      </c>
+      <c r="F164" t="s">
+        <v>43</v>
+      </c>
+      <c r="I164" t="s">
+        <v>509</v>
+      </c>
+      <c r="J164" t="s">
+        <v>286</v>
+      </c>
+      <c r="L164" t="s">
+        <v>290</v>
+      </c>
+      <c r="M164" t="s">
+        <v>291</v>
+      </c>
+      <c r="N164" t="s">
+        <v>292</v>
+      </c>
+      <c r="O164" t="s">
+        <v>337</v>
+      </c>
+      <c r="P164" t="s">
+        <v>337</v>
+      </c>
+      <c r="Q164" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>1</v>
+      </c>
+      <c r="B165" t="s">
+        <v>339</v>
+      </c>
+      <c r="C165" t="s">
+        <v>340</v>
+      </c>
+      <c r="E165" t="s">
+        <v>288</v>
+      </c>
+      <c r="F165" t="s">
+        <v>43</v>
+      </c>
+      <c r="I165" t="s">
+        <v>510</v>
+      </c>
+      <c r="J165" t="s">
+        <v>339</v>
+      </c>
+      <c r="L165" t="s">
+        <v>341</v>
+      </c>
+      <c r="M165" t="s">
+        <v>342</v>
+      </c>
+      <c r="N165" t="s">
+        <v>343</v>
+      </c>
+      <c r="O165" t="s">
+        <v>340</v>
+      </c>
+      <c r="P165" t="s">
+        <v>340</v>
+      </c>
+      <c r="Q165" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="166" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>1</v>
+      </c>
+      <c r="B166" t="s">
+        <v>339</v>
+      </c>
+      <c r="C166" t="s">
+        <v>344</v>
+      </c>
+      <c r="E166" t="s">
+        <v>288</v>
+      </c>
+      <c r="F166" t="s">
+        <v>43</v>
+      </c>
+      <c r="I166" t="s">
+        <v>511</v>
+      </c>
+      <c r="J166" t="s">
+        <v>339</v>
+      </c>
+      <c r="L166" t="s">
+        <v>341</v>
+      </c>
+      <c r="M166" t="s">
+        <v>342</v>
+      </c>
+      <c r="N166" t="s">
+        <v>343</v>
+      </c>
+      <c r="O166" t="s">
+        <v>344</v>
+      </c>
+      <c r="P166" t="s">
+        <v>344</v>
+      </c>
+      <c r="Q166" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="167" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>1</v>
+      </c>
+      <c r="B167" t="s">
+        <v>339</v>
+      </c>
+      <c r="C167" t="s">
+        <v>345</v>
+      </c>
+      <c r="E167" t="s">
+        <v>288</v>
+      </c>
+      <c r="F167" t="s">
+        <v>43</v>
+      </c>
+      <c r="I167" t="s">
+        <v>512</v>
+      </c>
+      <c r="J167" t="s">
+        <v>339</v>
+      </c>
+      <c r="L167" t="s">
+        <v>341</v>
+      </c>
+      <c r="M167" t="s">
+        <v>342</v>
+      </c>
+      <c r="N167" t="s">
+        <v>343</v>
+      </c>
+      <c r="O167" t="s">
+        <v>345</v>
+      </c>
+      <c r="P167" t="s">
+        <v>345</v>
+      </c>
+      <c r="Q167" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="168" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>1</v>
+      </c>
+      <c r="B168" t="s">
+        <v>339</v>
+      </c>
+      <c r="C168" t="s">
+        <v>513</v>
+      </c>
+      <c r="E168" t="s">
+        <v>288</v>
+      </c>
+      <c r="F168" t="s">
+        <v>43</v>
+      </c>
+      <c r="I168" t="s">
+        <v>514</v>
+      </c>
+      <c r="J168" t="s">
+        <v>339</v>
+      </c>
+      <c r="L168" t="s">
+        <v>341</v>
+      </c>
+      <c r="M168" t="s">
+        <v>342</v>
+      </c>
+      <c r="N168" t="s">
+        <v>343</v>
+      </c>
+      <c r="O168" t="s">
+        <v>513</v>
+      </c>
+      <c r="P168" t="s">
+        <v>513</v>
+      </c>
+      <c r="Q168" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="169" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>1</v>
+      </c>
+      <c r="B169" t="s">
+        <v>339</v>
+      </c>
+      <c r="C169" t="s">
+        <v>346</v>
+      </c>
+      <c r="E169" t="s">
+        <v>288</v>
+      </c>
+      <c r="F169" t="s">
+        <v>43</v>
+      </c>
+      <c r="I169" t="s">
+        <v>515</v>
+      </c>
+      <c r="J169" t="s">
+        <v>339</v>
+      </c>
+      <c r="L169" t="s">
+        <v>341</v>
+      </c>
+      <c r="M169" t="s">
+        <v>342</v>
+      </c>
+      <c r="N169" t="s">
+        <v>343</v>
+      </c>
+      <c r="O169" t="s">
+        <v>346</v>
+      </c>
+      <c r="P169" t="s">
+        <v>346</v>
+      </c>
+      <c r="Q169" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="170" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>1</v>
+      </c>
+      <c r="B170" t="s">
+        <v>339</v>
+      </c>
+      <c r="C170" t="s">
+        <v>347</v>
+      </c>
+      <c r="E170" t="s">
+        <v>288</v>
+      </c>
+      <c r="F170" t="s">
+        <v>43</v>
+      </c>
+      <c r="I170" t="s">
+        <v>516</v>
+      </c>
+      <c r="J170" t="s">
+        <v>339</v>
+      </c>
+      <c r="L170" t="s">
+        <v>341</v>
+      </c>
+      <c r="M170" t="s">
+        <v>342</v>
+      </c>
+      <c r="N170" t="s">
+        <v>343</v>
+      </c>
+      <c r="O170" t="s">
+        <v>347</v>
+      </c>
+      <c r="P170" t="s">
+        <v>347</v>
+      </c>
+      <c r="Q170" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="171" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>1</v>
+      </c>
+      <c r="B171" t="s">
+        <v>339</v>
+      </c>
+      <c r="C171" t="s">
+        <v>348</v>
+      </c>
+      <c r="E171" t="s">
+        <v>288</v>
+      </c>
+      <c r="F171" t="s">
+        <v>43</v>
+      </c>
+      <c r="I171" t="s">
+        <v>517</v>
+      </c>
+      <c r="J171" t="s">
+        <v>339</v>
+      </c>
+      <c r="L171" t="s">
+        <v>341</v>
+      </c>
+      <c r="M171" t="s">
+        <v>342</v>
+      </c>
+      <c r="N171" t="s">
+        <v>343</v>
+      </c>
+      <c r="O171" t="s">
+        <v>348</v>
+      </c>
+      <c r="P171" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q171" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="172" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>1</v>
+      </c>
+      <c r="B172" t="s">
+        <v>339</v>
+      </c>
+      <c r="C172" t="s">
+        <v>349</v>
+      </c>
+      <c r="E172" t="s">
+        <v>288</v>
+      </c>
+      <c r="F172" t="s">
+        <v>43</v>
+      </c>
+      <c r="I172" t="s">
+        <v>518</v>
+      </c>
+      <c r="J172" t="s">
+        <v>339</v>
+      </c>
+      <c r="L172" t="s">
+        <v>341</v>
+      </c>
+      <c r="M172" t="s">
+        <v>342</v>
+      </c>
+      <c r="N172" t="s">
+        <v>343</v>
+      </c>
+      <c r="O172" t="s">
+        <v>349</v>
+      </c>
+      <c r="P172" t="s">
+        <v>349</v>
+      </c>
+      <c r="Q172" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="173" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>1</v>
+      </c>
+      <c r="B173" t="s">
+        <v>339</v>
+      </c>
+      <c r="C173" t="s">
+        <v>350</v>
+      </c>
+      <c r="E173" t="s">
+        <v>288</v>
+      </c>
+      <c r="F173" t="s">
+        <v>43</v>
+      </c>
+      <c r="I173" t="s">
+        <v>519</v>
+      </c>
+      <c r="J173" t="s">
+        <v>339</v>
+      </c>
+      <c r="L173" t="s">
+        <v>341</v>
+      </c>
+      <c r="M173" t="s">
+        <v>342</v>
+      </c>
+      <c r="N173" t="s">
+        <v>343</v>
+      </c>
+      <c r="O173" t="s">
+        <v>350</v>
+      </c>
+      <c r="P173" t="s">
+        <v>350</v>
+      </c>
+      <c r="Q173" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="174" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>1</v>
+      </c>
+      <c r="B174" t="s">
+        <v>339</v>
+      </c>
+      <c r="C174" t="s">
+        <v>351</v>
+      </c>
+      <c r="E174" t="s">
+        <v>288</v>
+      </c>
+      <c r="F174" t="s">
+        <v>43</v>
+      </c>
+      <c r="I174" t="s">
+        <v>520</v>
+      </c>
+      <c r="J174" t="s">
+        <v>339</v>
+      </c>
+      <c r="L174" t="s">
+        <v>341</v>
+      </c>
+      <c r="M174" t="s">
+        <v>342</v>
+      </c>
+      <c r="N174" t="s">
+        <v>343</v>
+      </c>
+      <c r="O174" t="s">
+        <v>351</v>
+      </c>
+      <c r="P174" t="s">
+        <v>351</v>
+      </c>
+      <c r="Q174" t="s">
+        <v>351</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="B44:B91">
-    <cfRule type="duplicateValues" dxfId="20" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C44:C52">
-    <cfRule type="duplicateValues" dxfId="19" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C54:C58 C60:C62">
-    <cfRule type="duplicateValues" dxfId="18" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C63:C75">
-    <cfRule type="duplicateValues" dxfId="17" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C76">
-    <cfRule type="duplicateValues" dxfId="16" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C78:C89">
-    <cfRule type="duplicateValues" dxfId="15" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C92 C94">
-    <cfRule type="duplicateValues" dxfId="14" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H53">
-    <cfRule type="duplicateValues" dxfId="13" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H59">
-    <cfRule type="duplicateValues" dxfId="12" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H77">
-    <cfRule type="duplicateValues" dxfId="11" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H90">
-    <cfRule type="duplicateValues" dxfId="10" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I44:I52">
-    <cfRule type="duplicateValues" dxfId="9" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I54:I58">
-    <cfRule type="duplicateValues" dxfId="8" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I63:I75">
-    <cfRule type="duplicateValues" dxfId="7" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I76">
-    <cfRule type="duplicateValues" dxfId="6" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I78:I89">
-    <cfRule type="duplicateValues" dxfId="5" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I92 I94">
-    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J44:J76">
-    <cfRule type="duplicateValues" dxfId="3" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J77">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J78:J89">
-    <cfRule type="duplicateValues" dxfId="1" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J90:J91">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C140 C142">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I140 I142">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
